--- a/public/exports/29189900.xlsx
+++ b/public/exports/29189900.xlsx
@@ -29394,7 +29394,7 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914906</t>
+          <t xml:space="preserve">311914928</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">

--- a/public/exports/29189900.xlsx
+++ b/public/exports/29189900.xlsx
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612022</t>
+          <t xml:space="preserve">311611988</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650293</t>
+          <t xml:space="preserve">311650183</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650293</t>
+          <t xml:space="preserve">311650183</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650293</t>
+          <t xml:space="preserve">311650183</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650293</t>
+          <t xml:space="preserve">311650183</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686424</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686427</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686425</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686428</t>
+          <t xml:space="preserve">311686426</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713864</t>
+          <t xml:space="preserve">311713843</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727078</t>
+          <t xml:space="preserve">311727076</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -25374,7 +25374,7 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807599</t>
+          <t xml:space="preserve">311807605</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807599</t>
+          <t xml:space="preserve">311807605</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807599</t>
+          <t xml:space="preserve">311807605</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807599</t>
+          <t xml:space="preserve">311807605</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914928</t>
+          <t xml:space="preserve">311914906</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">

--- a/public/exports/29189900.xlsx
+++ b/public/exports/29189900.xlsx
@@ -2589,7 +2589,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053074</t>
+          <t xml:space="preserve">200053064</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053074</t>
+          <t xml:space="preserve">200053064</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056978</t>
+          <t xml:space="preserve">200056974</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686424</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686426</t>
+          <t xml:space="preserve">311686425</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -19034,12 +19034,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727118</t>
+          <t xml:space="preserve">311727076</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727118</t>
+          <t xml:space="preserve">311727076</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -19164,12 +19164,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727118</t>
+          <t xml:space="preserve">311727076</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727078</t>
+          <t xml:space="preserve">311727076</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -19294,12 +19294,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727118</t>
+          <t xml:space="preserve">311727076</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -19359,12 +19359,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727118</t>
+          <t xml:space="preserve">311727076</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24559,12 +24559,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t xml:space="preserve">311779120</t>
+          <t xml:space="preserve">311779113</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -31839,7 +31839,7 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914906</t>
+          <t xml:space="preserve">311914896</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
